--- a/src/attributions/attributions_ig_traj_245.xlsx
+++ b/src/attributions/attributions_ig_traj_245.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG3"/>
+  <dimension ref="A1:GG11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1002,25 +1002,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.2960463733789755</v>
+        <v>0.7433800762288225</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5268038223632835</v>
+        <v>-0.07969354829845028</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03699289732677558</v>
+        <v>-0.4143161052062781</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -1029,70 +1029,70 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.2316772413073387</v>
+        <v>0.7538009240520056</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4651552248599837</v>
+        <v>-0.268239996333881</v>
       </c>
       <c r="N2" t="n">
-        <v>0.07059064002808547</v>
+        <v>-0.4486206482501759</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.122620650268001</v>
+        <v>-0.01386021754679653</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0.04448183281658329</v>
+        <v>-0.2766040057918855</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.03226813065433129</v>
+        <v>-0.2260442409402977</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z2" t="n">
         <v>-0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.1127687417990083</v>
+        <v>0.2479752421047699</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.03456545275427186</v>
+        <v>-0.1967393264902413</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.02316182269749729</v>
+        <v>0.2472916384724182</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -1104,55 +1104,55 @@
         <v>-0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.08438974793801785</v>
+        <v>0.244271237659834</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.02922921718039302</v>
+        <v>-0.1821586868562949</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.1018657185731441</v>
+        <v>0.3278935537630291</v>
       </c>
       <c r="AP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.3121402356021427</v>
+        <v>0.6053172215718958</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.2377078252830225</v>
+        <v>-0.0458250372030109</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.01174651981495749</v>
+        <v>-0.259842929423772</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
@@ -1161,19 +1161,19 @@
         <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.1106539185139866</v>
+        <v>0.2138416499137602</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.156656338322448</v>
+        <v>0.06044387224743963</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.1157969281835891</v>
+        <v>-0.1241401069053515</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1188,46 +1188,46 @@
         <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM2" t="n">
-        <v>-0.02629712294032379</v>
+        <v>-0.06889025947900551</v>
       </c>
       <c r="BN2" t="n">
         <v>-0</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.01306663470683733</v>
+        <v>-0.1338634143433003</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0.1700808674577257</v>
+        <v>0.2020919025528532</v>
       </c>
       <c r="BQ2" t="n">
         <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU2" t="n">
         <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>-0.1489505816804149</v>
+        <v>0.3557111404164162</v>
       </c>
       <c r="BW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.0761619560969035</v>
+        <v>-0.2134823211291341</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.06191889759765432</v>
+        <v>-0.1778675943314897</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1236,7 +1236,7 @@
         <v>-0</v>
       </c>
       <c r="CB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC2" t="n">
         <v>0</v>
@@ -1245,73 +1245,73 @@
         <v>-0</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.0614294541186783</v>
+        <v>-0.3838461875966683</v>
       </c>
       <c r="CF2" t="n">
         <v>-0</v>
       </c>
       <c r="CG2" t="n">
-        <v>-0.09854279758783759</v>
+        <v>0.05982516142547619</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.01933217163557499</v>
+        <v>0.04386237337245069</v>
       </c>
       <c r="CI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ2" t="n">
         <v>0</v>
       </c>
       <c r="CK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.009673849950292334</v>
+        <v>-0.1139203649435021</v>
       </c>
       <c r="CO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>-0.00816328791996045</v>
+        <v>0.1248309474729341</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.03468253144229033</v>
+        <v>-0.130126228418012</v>
       </c>
       <c r="CR2" t="n">
         <v>-0</v>
       </c>
       <c r="CS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU2" t="n">
         <v>-0</v>
       </c>
       <c r="CV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.07565791447210174</v>
+        <v>-0.3656725127187421</v>
       </c>
       <c r="CX2" t="n">
         <v>0</v>
       </c>
       <c r="CY2" t="n">
-        <v>-0.09168833644779097</v>
+        <v>0.07258896014523786</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.007307234473590525</v>
+        <v>0.0748557422907082</v>
       </c>
       <c r="DA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB2" t="n">
         <v>-0</v>
@@ -1320,79 +1320,79 @@
         <v>-0</v>
       </c>
       <c r="DD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.2203399921105718</v>
+        <v>-0.2827520306447179</v>
       </c>
       <c r="DG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH2" t="n">
-        <v>-0.06479944268121397</v>
+        <v>-0.06394207992293978</v>
       </c>
       <c r="DI2" t="n">
-        <v>-0.01360764237365175</v>
+        <v>0.01687113449174454</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK2" t="n">
         <v>-0</v>
       </c>
       <c r="DL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN2" t="n">
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.006747358222326433</v>
+        <v>-0.3124424488503906</v>
       </c>
       <c r="DP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.02854774387101981</v>
+        <v>0.2337110339409491</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.04536958010288934</v>
+        <v>0.1610493526701908</v>
       </c>
       <c r="DS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU2" t="n">
         <v>-0</v>
       </c>
       <c r="DV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.07493758384032732</v>
+        <v>-0.06007809875150456</v>
       </c>
       <c r="DY2" t="n">
         <v>-0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>-0.08883239768176981</v>
+        <v>-0.02578457605991687</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.04430560910768386</v>
+        <v>-0.1617096938440826</v>
       </c>
       <c r="EB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC2" t="n">
         <v>-0</v>
@@ -1401,22 +1401,22 @@
         <v>0</v>
       </c>
       <c r="EE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF2" t="n">
         <v>-0</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.04405865593471068</v>
+        <v>-0.3083252984308573</v>
       </c>
       <c r="EH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.1233349463462246</v>
+        <v>0.2392373821164902</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.04718535020630139</v>
+        <v>0.1320883571821137</v>
       </c>
       <c r="EK2" t="n">
         <v>-0</v>
@@ -1428,85 +1428,85 @@
         <v>0</v>
       </c>
       <c r="EN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP2" t="n">
-        <v>-0.08545463168014399</v>
+        <v>0.1035549037610283</v>
       </c>
       <c r="EQ2" t="n">
         <v>-0</v>
       </c>
       <c r="ER2" t="n">
-        <v>-0.04345999815872956</v>
+        <v>0.02004952176443208</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.008592766471658466</v>
+        <v>-0.002645967427856241</v>
       </c>
       <c r="ET2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU2" t="n">
         <v>0</v>
       </c>
       <c r="EV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW2" t="n">
         <v>0</v>
       </c>
       <c r="EX2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.07585134005944467</v>
+        <v>-0.4243713920891692</v>
       </c>
       <c r="EZ2" t="n">
         <v>-0</v>
       </c>
       <c r="FA2" t="n">
-        <v>-0.09040075738863187</v>
+        <v>0.07264280127064505</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.01667877379403799</v>
+        <v>0.06717655561025011</v>
       </c>
       <c r="FC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG2" t="n">
         <v>-0</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.02409076984794263</v>
+        <v>-0.2100600381432484</v>
       </c>
       <c r="FI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ2" t="n">
-        <v>-0.0184632593962781</v>
+        <v>0.1920665198666135</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.004901368697501501</v>
+        <v>-0.09719690136356801</v>
       </c>
       <c r="FL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM2" t="n">
         <v>0</v>
       </c>
       <c r="FN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO2" t="n">
         <v>-0</v>
@@ -1515,49 +1515,49 @@
         <v>-0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.04406105770087931</v>
+        <v>-0.3071716589163544</v>
       </c>
       <c r="FR2" t="n">
         <v>0</v>
       </c>
       <c r="FS2" t="n">
-        <v>-0.05970442660625477</v>
+        <v>0.338038581557128</v>
       </c>
       <c r="FT2" t="n">
-        <v>-0.00934797519253004</v>
+        <v>0.4774788902368929</v>
       </c>
       <c r="FU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW2" t="n">
         <v>-0</v>
       </c>
       <c r="FX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY2" t="n">
         <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.03240683425055917</v>
+        <v>-0.1724357324032615</v>
       </c>
       <c r="GA2" t="n">
         <v>0</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.04675043660985335</v>
+        <v>0.05144122502789127</v>
       </c>
       <c r="GC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD2" t="n">
         <v>0</v>
       </c>
       <c r="GE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF2" t="n">
         <v>-0</v>
@@ -1571,103 +1571,103 @@
         <v>0</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>-0.2628537579413622</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.1055417828086552</v>
       </c>
       <c r="E3" t="n">
-        <v>-0</v>
+        <v>0.08052724552830305</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-0.2028453130059719</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.168244435332824</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0.1481248792069367</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-0.06693319592578439</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.02961852358961999</v>
       </c>
       <c r="W3" t="n">
-        <v>-0</v>
+        <v>-0.01253580606990309</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>-0.003643229082343925</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>0.1472288935097706</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0</v>
+        <v>-0.1099234453851387</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1676,49 +1676,49 @@
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>-0.1365681452988129</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>0.02597110012516378</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0</v>
+        <v>-0.212212186769747</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS3" t="n">
         <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>-0.37391759686137</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>0.1341670038908112</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0</v>
+        <v>0.03390012146465593</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1730,52 +1730,52 @@
         <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>0.02860152245105128</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>0.05490878004266257</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0</v>
+        <v>0.1172533100750635</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>0.09435375811658782</v>
       </c>
       <c r="BN3" t="n">
         <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>0.08303388229750441</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0</v>
+        <v>-0.04617161234153407</v>
       </c>
       <c r="BQ3" t="n">
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS3" t="n">
         <v>0</v>
@@ -1787,43 +1787,43 @@
         <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>-0.21263420347152</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>0.06740378465434772</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0</v>
+        <v>-0.002080648570801017</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA3" t="n">
         <v>0</v>
       </c>
       <c r="CB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD3" t="n">
         <v>0</v>
       </c>
       <c r="CE3" t="n">
-        <v>0</v>
+        <v>0.1844666233474835</v>
       </c>
       <c r="CF3" t="n">
         <v>0</v>
       </c>
       <c r="CG3" t="n">
-        <v>0</v>
+        <v>-0.05625804921672842</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0</v>
+        <v>-0.01038388877842425</v>
       </c>
       <c r="CI3" t="n">
         <v>0</v>
@@ -1832,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="CK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL3" t="n">
         <v>0</v>
@@ -1841,16 +1841,16 @@
         <v>0</v>
       </c>
       <c r="CN3" t="n">
-        <v>0</v>
+        <v>0.03183365166468763</v>
       </c>
       <c r="CO3" t="n">
         <v>0</v>
       </c>
       <c r="CP3" t="n">
-        <v>0</v>
+        <v>-0.09118623915778856</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0</v>
+        <v>-0.005140887371599748</v>
       </c>
       <c r="CR3" t="n">
         <v>0</v>
@@ -1868,70 +1868,70 @@
         <v>0</v>
       </c>
       <c r="CW3" t="n">
-        <v>0</v>
+        <v>0.2000234233485225</v>
       </c>
       <c r="CX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY3" t="n">
-        <v>0</v>
+        <v>-0.06569654874223389</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0</v>
+        <v>-0.03264278124401966</v>
       </c>
       <c r="DA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC3" t="n">
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF3" t="n">
-        <v>0</v>
+        <v>0.05793629579500679</v>
       </c>
       <c r="DG3" t="n">
         <v>0</v>
       </c>
       <c r="DH3" t="n">
-        <v>0</v>
+        <v>0.008146194572403304</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0</v>
+        <v>0.004007709000574946</v>
       </c>
       <c r="DJ3" t="n">
         <v>0</v>
       </c>
       <c r="DK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO3" t="n">
-        <v>0</v>
+        <v>0.09153593336165917</v>
       </c>
       <c r="DP3" t="n">
         <v>0</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0</v>
+        <v>-0.02209349040497874</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0</v>
+        <v>0.01219145095554745</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -1940,25 +1940,25 @@
         <v>0</v>
       </c>
       <c r="DU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>0</v>
+        <v>0.08555549946516705</v>
       </c>
       <c r="DY3" t="n">
         <v>0</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>-0.00816355098716391</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0</v>
+        <v>0.02277042539239598</v>
       </c>
       <c r="EB3" t="n">
         <v>0</v>
@@ -1967,61 +1967,61 @@
         <v>0</v>
       </c>
       <c r="ED3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE3" t="n">
         <v>0</v>
       </c>
       <c r="EF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG3" t="n">
-        <v>0</v>
+        <v>0.1869526032437643</v>
       </c>
       <c r="EH3" t="n">
         <v>0</v>
       </c>
       <c r="EI3" t="n">
-        <v>0</v>
+        <v>-0.05981905789488771</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0</v>
+        <v>-0.03014251098666013</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL3" t="n">
         <v>0</v>
       </c>
       <c r="EM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN3" t="n">
         <v>0</v>
       </c>
       <c r="EO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP3" t="n">
-        <v>0</v>
+        <v>-0.1051230236316615</v>
       </c>
       <c r="EQ3" t="n">
         <v>0</v>
       </c>
       <c r="ER3" t="n">
-        <v>0</v>
+        <v>-0.004423283710990409</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0</v>
+        <v>-0.02096494924470798</v>
       </c>
       <c r="ET3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW3" t="n">
         <v>0</v>
@@ -2030,16 +2030,16 @@
         <v>0</v>
       </c>
       <c r="EY3" t="n">
-        <v>0</v>
+        <v>0.225606893973079</v>
       </c>
       <c r="EZ3" t="n">
         <v>0</v>
       </c>
       <c r="FA3" t="n">
-        <v>0</v>
+        <v>-0.07870865156872257</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0</v>
+        <v>-0.005782021997221783</v>
       </c>
       <c r="FC3" t="n">
         <v>0</v>
@@ -2048,52 +2048,52 @@
         <v>0</v>
       </c>
       <c r="FE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF3" t="n">
         <v>0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH3" t="n">
-        <v>0</v>
+        <v>0.09609054885461389</v>
       </c>
       <c r="FI3" t="n">
         <v>0</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0</v>
+        <v>0.09155115650680434</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0</v>
+        <v>-0.01847368768181014</v>
       </c>
       <c r="FL3" t="n">
         <v>0</v>
       </c>
       <c r="FM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN3" t="n">
         <v>0</v>
       </c>
       <c r="FO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP3" t="n">
         <v>0</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0</v>
+        <v>0.206357875578024</v>
       </c>
       <c r="FR3" t="n">
         <v>0</v>
       </c>
       <c r="FS3" t="n">
-        <v>0</v>
+        <v>0.06488647954864374</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0</v>
+        <v>-0.1412046321392382</v>
       </c>
       <c r="FU3" t="n">
         <v>0</v>
@@ -2105,25 +2105,25 @@
         <v>0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0</v>
+        <v>0.2058395414240731</v>
       </c>
       <c r="GA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB3" t="n">
-        <v>0</v>
+        <v>-0.006978728433282276</v>
       </c>
       <c r="GC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE3" t="n">
         <v>0</v>
@@ -2132,6 +2132,4558 @@
         <v>0</v>
       </c>
       <c r="GG3" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.249027327547678</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.1039970860381959</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.005102570623100672</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.1116850877672301</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.2992648488818383</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-0.09888741878714856</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-0.07156062136863897</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-0.07684771733471335</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.1042140587440149</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-0.07546360958350587</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-0.09181681117021052</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-0.05424444718777578</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-0.05733282575330979</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-0.1375405768613344</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-0.02843048848614434</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.05376093495995564</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.07620863324794441</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>-0.07211119139797018</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.02997404418316774</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-0.03724727579007161</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.3603495274571381</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>-0.1528886722530149</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>-0.2018129319214596</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>-0.166437506254554</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>-0.0415745301318473</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>-0.07021492633720067</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0.005112754921982095</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>-0.09785357523193189</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.03624617049247352</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0.07958018939536891</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>0.01349651784040254</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>0.0104093269296282</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>0.1950483753457889</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>-0.09039625522185822</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>-0.06764743250590358</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>-0.1303099297385667</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>-0.08965416294631859</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>0.09017318740581234</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>-0.003744394432621063</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>0.04262726363915661</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>-0.02033285749113068</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>0.08425727299422703</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>0.04645953571720601</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>0.01536426539140878</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>-0.097334941253773</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>0.1100057958453151</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>0.002864686545440955</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>0.07032382080882771</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>-0.05420950208610163</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>0.023444112619843</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>0.009200420788710457</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>0.02488552882447583</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>0.0006608814544339273</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>0.01599843077978104</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>-0.1030395015917234</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>-0.008142391488326442</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX4" t="n">
+        <v>-0.03421514678468975</v>
+      </c>
+      <c r="DY4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ4" t="n">
+        <v>0.07825713762211674</v>
+      </c>
+      <c r="EA4" t="n">
+        <v>0.005783623328588454</v>
+      </c>
+      <c r="EB4" t="n">
+        <v>-0.03475952361142329</v>
+      </c>
+      <c r="EC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG4" t="n">
+        <v>-0.0806831319280388</v>
+      </c>
+      <c r="EH4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI4" t="n">
+        <v>0.09199625827097606</v>
+      </c>
+      <c r="EJ4" t="n">
+        <v>0.0193243416531384</v>
+      </c>
+      <c r="EK4" t="n">
+        <v>-0.036272286935615</v>
+      </c>
+      <c r="EL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP4" t="n">
+        <v>-0.03450502888511527</v>
+      </c>
+      <c r="EQ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER4" t="n">
+        <v>0.0609551997732563</v>
+      </c>
+      <c r="ES4" t="n">
+        <v>0.01752867232073513</v>
+      </c>
+      <c r="ET4" t="n">
+        <v>0.07581684700087714</v>
+      </c>
+      <c r="EU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY4" t="n">
+        <v>-0.1014948293199905</v>
+      </c>
+      <c r="EZ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA4" t="n">
+        <v>0.1283210047609431</v>
+      </c>
+      <c r="FB4" t="n">
+        <v>-0.01515149501166281</v>
+      </c>
+      <c r="FC4" t="n">
+        <v>0.05657620585043636</v>
+      </c>
+      <c r="FD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH4" t="n">
+        <v>0.09704186372855188</v>
+      </c>
+      <c r="FI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ4" t="n">
+        <v>0.08967153372796453</v>
+      </c>
+      <c r="FK4" t="n">
+        <v>0.007460468439977981</v>
+      </c>
+      <c r="FL4" t="n">
+        <v>0.144217944672616</v>
+      </c>
+      <c r="FM4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ4" t="n">
+        <v>0.01292869213476163</v>
+      </c>
+      <c r="FR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS4" t="n">
+        <v>0.1511968485040224</v>
+      </c>
+      <c r="FT4" t="n">
+        <v>-0.04224949618086624</v>
+      </c>
+      <c r="FU4" t="n">
+        <v>0.004225501040959629</v>
+      </c>
+      <c r="FV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ4" t="n">
+        <v>-0.02898381804717588</v>
+      </c>
+      <c r="GA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB4" t="n">
+        <v>0.03407079336371571</v>
+      </c>
+      <c r="GC4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD4" t="n">
+        <v>0.07627047447481823</v>
+      </c>
+      <c r="GE4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG4" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.2215322855406511</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.08079226242696226</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.02016813462993244</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.2633574869799849</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-0.0892453523440256</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0.05682904430409131</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.05709312059146299</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-0.02100990021384219</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-0.0298876619281884</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-0.0121731531045291</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-0.09044999853162897</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-0.01320952748630769</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.06948722428070421</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-0.05501460077428859</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.07577286768521159</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0.209726271567324</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>-0.05016551727715616</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>-0.1217762517991149</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>-0.0002954124804574009</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>-0.03481541974007678</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>-0.03824798642571543</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>-0.007816482788425914</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0.02128912590302387</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0.05874445731005184</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>0.1477717059555307</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>-0.04455999138645179</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>-0.02206597306520466</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>-0.08643282900751541</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0.06991048155246572</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0.0007775842720287341</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>-0.03656406692152463</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>0.09783575108328708</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>0.0178055101731727</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>-0.08397317352705837</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>0.08032853063722784</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>0.005926514242300427</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>-0.04520296707651449</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>0.017640048201015</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>-0.04859064878530735</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>-0.03716930061347866</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>-0.07453626424573065</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>-0.04941527942768822</v>
+      </c>
+      <c r="DS5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>-0.02180477969716717</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ5" t="n">
+        <v>0.03619524976552568</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>-0.02380579988771007</v>
+      </c>
+      <c r="EB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG5" t="n">
+        <v>-0.06136348149235122</v>
+      </c>
+      <c r="EH5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI5" t="n">
+        <v>0.04812467311105083</v>
+      </c>
+      <c r="EJ5" t="n">
+        <v>0.03369574305309238</v>
+      </c>
+      <c r="EK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP5" t="n">
+        <v>-0.02257998965145745</v>
+      </c>
+      <c r="EQ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER5" t="n">
+        <v>-0.001199203358449382</v>
+      </c>
+      <c r="ES5" t="n">
+        <v>-0.00859310801383986</v>
+      </c>
+      <c r="ET5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY5" t="n">
+        <v>-0.09143585770166456</v>
+      </c>
+      <c r="EZ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA5" t="n">
+        <v>0.09278531423937351</v>
+      </c>
+      <c r="FB5" t="n">
+        <v>-0.01538801888340146</v>
+      </c>
+      <c r="FC5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH5" t="n">
+        <v>0.08445161908174242</v>
+      </c>
+      <c r="FI5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ5" t="n">
+        <v>0.06760642479062147</v>
+      </c>
+      <c r="FK5" t="n">
+        <v>-0.01357754812205016</v>
+      </c>
+      <c r="FL5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ5" t="n">
+        <v>0.00121688941597181</v>
+      </c>
+      <c r="FR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS5" t="n">
+        <v>0.0929289061692383</v>
+      </c>
+      <c r="FT5" t="n">
+        <v>-0.01806901786159286</v>
+      </c>
+      <c r="FU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ5" t="n">
+        <v>-0.06488978468003571</v>
+      </c>
+      <c r="GA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB5" t="n">
+        <v>0.02264964297637794</v>
+      </c>
+      <c r="GC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GE5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.3592665774559661</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.0124110029667905</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.3185349832123135</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.4887661062873814</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.06469976493982263</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-0.408413885587264</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.1348631657901264</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.08997640117938424</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0.0684747771039094</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-0.02099978615454538</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-0.2762934213857937</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.09734500500817471</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.1238131272451377</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-0.05949332035183696</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-0.08840890567862766</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.6463937434838852</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-0.2885792206392588</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>-0.1997911008837412</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-0.1126946781311991</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-0.02566080516115521</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>-0.03750661578764619</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.1267599079000587</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0.07541834802918621</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0.04127890339293192</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>0.3700263990427802</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>-0.03550810160760057</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>-0.182342771419829</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>-0.1485052524197779</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0.03170414698786368</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0.10798569496285</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>-0.1446464043346002</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>0.1146393546140499</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>0.02857141539470635</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>-0.1404595684646018</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>0.01524570695447108</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>0.1398991042049428</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>-0.1112803389875733</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>-0.05844885863992825</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>0.08664942347776897</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>-0.08910546458876216</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>-0.0005639195766592671</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>0.1093306977228302</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>-0.06335993665451449</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>-0.007427109329146578</v>
+      </c>
+      <c r="EB6" t="n">
+        <v>0.0352411578116134</v>
+      </c>
+      <c r="EC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG6" t="n">
+        <v>-0.03320885329837635</v>
+      </c>
+      <c r="EH6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ6" t="n">
+        <v>-0.02386518241475493</v>
+      </c>
+      <c r="EK6" t="n">
+        <v>0.02759106305415946</v>
+      </c>
+      <c r="EL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP6" t="n">
+        <v>-0.05758744597421768</v>
+      </c>
+      <c r="EQ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES6" t="n">
+        <v>-0.07571519355732911</v>
+      </c>
+      <c r="ET6" t="n">
+        <v>-0.008201805572983724</v>
+      </c>
+      <c r="EU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY6" t="n">
+        <v>-0.1689420317745762</v>
+      </c>
+      <c r="EZ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB6" t="n">
+        <v>-0.006821154732513475</v>
+      </c>
+      <c r="FC6" t="n">
+        <v>0.1216136351736869</v>
+      </c>
+      <c r="FD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH6" t="n">
+        <v>0.113972084665418</v>
+      </c>
+      <c r="FI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK6" t="n">
+        <v>-0.06401186692973805</v>
+      </c>
+      <c r="FL6" t="n">
+        <v>0.1740780511956319</v>
+      </c>
+      <c r="FM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ6" t="n">
+        <v>0.009837011797909613</v>
+      </c>
+      <c r="FR6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT6" t="n">
+        <v>-0.007780681991905951</v>
+      </c>
+      <c r="FU6" t="n">
+        <v>-0.0723317750183132</v>
+      </c>
+      <c r="FV6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ6" t="n">
+        <v>-0.02381991724614782</v>
+      </c>
+      <c r="GA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD6" t="n">
+        <v>0.1680208705088072</v>
+      </c>
+      <c r="GE6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.3451182324101872</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.02415007276200525</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.1423975481477552</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.4556398729406052</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0.1057542333602102</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.2037387679502438</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.0994621737550056</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-0.1181451646230026</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.01165391202914747</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-0.03181093238320283</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-0.2802260515972894</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-0.0004806981102348303</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.03391320067782991</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>-0.04382687751844315</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0.01800998439388342</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.490930550772916</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>-0.2412630341333792</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>-0.1060183635823349</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>-0.03244371999040717</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>-0.01743696709524062</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>-0.08854328880803962</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0.0555858806580355</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0.08095184223925117</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>-0.0353695774531211</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0.2645884054932645</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>-0.07607225122038919</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>-0.1065766498934343</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>-0.1128628071677499</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0.02940671068759908</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0.05005876308788209</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>-0.1176648399683078</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>0.0987659328249483</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>0.09696302121904032</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>-0.1132667735478171</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>0.008266387471978583</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>0.07134993351079165</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>-0.04182103570936625</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>-0.1773522024170269</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>0.05430905562071246</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>-0.006789881564130029</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>-0.06165173203514228</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0.07945600496514979</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>-0.0203989119697206</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>-0.0676568575607339</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>0.03633715307927934</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>-0.04598912915854268</v>
+      </c>
+      <c r="EH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ7" t="n">
+        <v>0.02204225341916105</v>
+      </c>
+      <c r="EK7" t="n">
+        <v>-0.009853383573066175</v>
+      </c>
+      <c r="EL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP7" t="n">
+        <v>-0.005227696832770167</v>
+      </c>
+      <c r="EQ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES7" t="n">
+        <v>-0.01220162516658875</v>
+      </c>
+      <c r="ET7" t="n">
+        <v>0.1364584260180013</v>
+      </c>
+      <c r="EU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY7" t="n">
+        <v>-0.130932432158351</v>
+      </c>
+      <c r="EZ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB7" t="n">
+        <v>-0.002061555924192711</v>
+      </c>
+      <c r="FC7" t="n">
+        <v>0.03987951912620769</v>
+      </c>
+      <c r="FD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH7" t="n">
+        <v>0.2075057372435904</v>
+      </c>
+      <c r="FI7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK7" t="n">
+        <v>-0.08888362194263089</v>
+      </c>
+      <c r="FL7" t="n">
+        <v>0.1169911234280748</v>
+      </c>
+      <c r="FM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ7" t="n">
+        <v>0.01095474566180105</v>
+      </c>
+      <c r="FR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT7" t="n">
+        <v>-0.02433236845990461</v>
+      </c>
+      <c r="FU7" t="n">
+        <v>-0.04959525460895942</v>
+      </c>
+      <c r="FV7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ7" t="n">
+        <v>-0.0392241248176862</v>
+      </c>
+      <c r="GA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD7" t="n">
+        <v>0.06229019800014492</v>
+      </c>
+      <c r="GE7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER9" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.3740873085411197</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.01212069175337799</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.1420221622722794</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.4550155857997566</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.1030346101625517</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.1872297503630286</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.08850790259557874</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.08737791763617689</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.01195679459117023</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-0.03445648712941773</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-0.2456376296061947</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.01208147322881906</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.03864887039576933</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>-0.03478953138166604</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0.004348853773135694</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0.4082565567656767</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>-0.2569226983256364</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>-0.1019174011449789</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>-0.007966828915457077</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0.003299825105484479</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>-0.06672767056896817</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0.03790515352353375</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0.05412149956945281</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>-0.02904912448350688</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>0.2284431608214726</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>-0.06484531704446789</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>-0.108101791999787</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>-0.106248834828522</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>0.02637823890535754</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>0.05235108424751526</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>-0.1167963372686887</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>0.1418910920064637</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>0.06948314519810558</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>-0.1042914444843911</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>0.01336787605902164</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>0.07393732256271993</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>-0.07613463879940778</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>-0.2088158290936235</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>0.0664830782668345</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>-0.01453139399809695</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>-0.04380413370108927</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>0.04598420032442908</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>-0.008128724834928856</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>-0.05739258479727879</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>0.02186635189298738</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>-0.04910027289638845</v>
+      </c>
+      <c r="EH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ10" t="n">
+        <v>0.009966225733988959</v>
+      </c>
+      <c r="EK10" t="n">
+        <v>-0.0008290111176221996</v>
+      </c>
+      <c r="EL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP10" t="n">
+        <v>-0.03263751016830274</v>
+      </c>
+      <c r="EQ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES10" t="n">
+        <v>-0.01666909488296208</v>
+      </c>
+      <c r="ET10" t="n">
+        <v>0.1081606505080878</v>
+      </c>
+      <c r="EU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY10" t="n">
+        <v>-0.1236182570442468</v>
+      </c>
+      <c r="EZ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB10" t="n">
+        <v>0.001119420975175839</v>
+      </c>
+      <c r="FC10" t="n">
+        <v>0.04480882699908054</v>
+      </c>
+      <c r="FD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH10" t="n">
+        <v>0.1682489665630392</v>
+      </c>
+      <c r="FI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK10" t="n">
+        <v>-0.08182097191585727</v>
+      </c>
+      <c r="FL10" t="n">
+        <v>0.1168730928665216</v>
+      </c>
+      <c r="FM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ10" t="n">
+        <v>0.001766033095943371</v>
+      </c>
+      <c r="FR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT10" t="n">
+        <v>-0.008890543018079875</v>
+      </c>
+      <c r="FU10" t="n">
+        <v>-0.02826654740530361</v>
+      </c>
+      <c r="FV10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ10" t="n">
+        <v>-0.03526500023485375</v>
+      </c>
+      <c r="GA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD10" t="n">
+        <v>0.06675703004937075</v>
+      </c>
+      <c r="GE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>0.2568294364946774</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.08360029537802897</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.1124021230301778</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.2217196001047798</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-0.007165351043765546</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-0.1079803910484537</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0.06928175277144705</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-0.04621480493013201</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.08056909819103956</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.0545615304003013</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-0.03953367418522752</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.05219803461472458</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.01635961694893267</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.0310684134670413</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.01725490832228489</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>-0.0180578642833223</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0.08887558904301493</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>-0.007113253437926324</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0.1617831854512066</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>-0.02019540684000256</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0.002295561210419389</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>-0.06679451029213296</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>-0.1113391538630767</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0.03653506681344443</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>-0.02642080760106553</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>-0.0702652693062062</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>-0.1104025499013803</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>-0.06422544393623388</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>0.007021126430780321</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>0.03115380220022167</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>0.01181028276288585</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>0.08373939567032432</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>-0.04380478783386278</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>-0.06726026660128644</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>0.004563328884568592</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>0.03598994833441783</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>-0.005146031250466448</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>-0.06032322361351384</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>0.01431398112090277</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>-0.03987372890085466</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>-0.05332094162376333</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>0.08169112504517606</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>0.02465871043844876</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>0.1237911810008313</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>0.06352424167544639</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>0.003466002153019663</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ11" t="n">
+        <v>-0.02625681375732344</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>0.0510532135942809</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO11" t="n">
+        <v>-0.03844273207820576</v>
+      </c>
+      <c r="EP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES11" t="n">
+        <v>0.006067814825159359</v>
+      </c>
+      <c r="ET11" t="n">
+        <v>0.04406886628997701</v>
+      </c>
+      <c r="EU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX11" t="n">
+        <v>-0.05967497713790787</v>
+      </c>
+      <c r="EY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB11" t="n">
+        <v>-0.006747037493913817</v>
+      </c>
+      <c r="FC11" t="n">
+        <v>0.04533085295682484</v>
+      </c>
+      <c r="FD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG11" t="n">
+        <v>0.127769368547643</v>
+      </c>
+      <c r="FH11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK11" t="n">
+        <v>-5.861337664423544e-05</v>
+      </c>
+      <c r="FL11" t="n">
+        <v>0.1059281336776556</v>
+      </c>
+      <c r="FM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP11" t="n">
+        <v>0.003074093359563177</v>
+      </c>
+      <c r="FQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT11" t="n">
+        <v>0.001590208613466223</v>
+      </c>
+      <c r="FU11" t="n">
+        <v>0.04096364891334509</v>
+      </c>
+      <c r="FV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY11" t="n">
+        <v>0.0725763631748053</v>
+      </c>
+      <c r="FZ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD11" t="n">
+        <v>0.07896609230274053</v>
+      </c>
+      <c r="GE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG11" t="n">
         <v>0</v>
       </c>
     </row>
